--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -23227,7 +23227,7 @@
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -23227,7 +23227,7 @@
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
